--- a/lang/tr/headTags.xlsx
+++ b/lang/tr/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1194</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1198</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2036">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2043">
   <si>
     <t>en</t>
   </si>
@@ -4948,6 +4948,18 @@
     <t>Shulker</t>
   </si>
   <si>
+    <t>Sift (Inspired)</t>
+  </si>
+  <si>
+    <t>Sift (İlham Kaynağı)</t>
+  </si>
+  <si>
+    <t>Sift (Vanilla)</t>
+  </si>
+  <si>
+    <t>Sift (Vanilya)</t>
+  </si>
+  <si>
     <t>Silent Hill</t>
   </si>
   <si>
@@ -5743,6 +5755,9 @@
     <t>ULTRAKILL</t>
   </si>
   <si>
+    <t>Umamusume</t>
+  </si>
+  <si>
     <t>Umineko - When They Cry</t>
   </si>
   <si>
@@ -6002,6 +6017,12 @@
   </si>
   <si>
     <t>Kış</t>
+  </si>
+  <si>
+    <t>Winter Drop</t>
+  </si>
+  <si>
+    <t>Kış Koleksiyonu</t>
   </si>
   <si>
     <t>Witcher</t>
@@ -6471,7 +6492,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1194"/>
+  <dimension ref="A1:B1198"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -14187,20 +14208,20 @@
         <v>1645</v>
       </c>
       <c r="B964" t="s">
-        <v>1645</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="965" spans="1:2">
       <c r="A965" t="s">
-        <v>1646</v>
+        <v>1647</v>
       </c>
       <c r="B965" t="s">
-        <v>1647</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="966" spans="1:2">
       <c r="A966" t="s">
-        <v>1648</v>
+        <v>1649</v>
       </c>
       <c r="B966" t="s">
         <v>1649</v>
@@ -14235,28 +14256,28 @@
         <v>1656</v>
       </c>
       <c r="B970" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="971" spans="1:2">
       <c r="A971" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
       <c r="B971" t="s">
-        <v>1657</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="972" spans="1:2">
       <c r="A972" t="s">
-        <v>1658</v>
+        <v>1660</v>
       </c>
       <c r="B972" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="973" spans="1:2">
       <c r="A973" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
       <c r="B973" t="s">
         <v>1661</v>
@@ -14299,36 +14320,36 @@
         <v>1670</v>
       </c>
       <c r="B978" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="979" spans="1:2">
       <c r="A979" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="B979" t="s">
-        <v>1671</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="980" spans="1:2">
       <c r="A980" t="s">
-        <v>1672</v>
+        <v>1674</v>
       </c>
       <c r="B980" t="s">
-        <v>1672</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="981" spans="1:2">
       <c r="A981" t="s">
-        <v>1673</v>
+        <v>1675</v>
       </c>
       <c r="B981" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="982" spans="1:2">
       <c r="A982" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="B982" t="s">
         <v>1676</v>
@@ -14379,36 +14400,36 @@
         <v>1687</v>
       </c>
       <c r="B988" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="989" spans="1:2">
       <c r="A989" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="B989" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="990" spans="1:2">
       <c r="A990" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="B990" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="991" spans="1:2">
       <c r="A991" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
       <c r="B991" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="992" spans="1:2">
       <c r="A992" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
       <c r="B992" t="s">
         <v>1694</v>
@@ -14419,28 +14440,28 @@
         <v>1695</v>
       </c>
       <c r="B993" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="994" spans="1:2">
       <c r="A994" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="B994" t="s">
-        <v>1696</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="995" spans="1:2">
       <c r="A995" t="s">
-        <v>1697</v>
+        <v>1699</v>
       </c>
       <c r="B995" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="996" spans="1:2">
       <c r="A996" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="B996" t="s">
         <v>1700</v>
@@ -14467,28 +14488,28 @@
         <v>1705</v>
       </c>
       <c r="B999" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="1000" spans="1:2">
       <c r="A1000" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="B1000" t="s">
-        <v>1706</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="1001" spans="1:2">
       <c r="A1001" t="s">
-        <v>1707</v>
+        <v>1709</v>
       </c>
       <c r="B1001" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="1002" spans="1:2">
       <c r="A1002" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="B1002" t="s">
         <v>1710</v>
@@ -14499,23 +14520,23 @@
         <v>1711</v>
       </c>
       <c r="B1003" t="s">
-        <v>1710</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="1004" spans="1:2">
       <c r="A1004" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
       <c r="B1004" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="1005" spans="1:2">
       <c r="A1005" t="s">
+        <v>1715</v>
+      </c>
+      <c r="B1005" t="s">
         <v>1714</v>
-      </c>
-      <c r="B1005" t="s">
-        <v>1715</v>
       </c>
     </row>
     <row r="1006" spans="1:2">
@@ -14531,20 +14552,20 @@
         <v>1718</v>
       </c>
       <c r="B1007" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="1008" spans="1:2">
       <c r="A1008" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
       <c r="B1008" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="1009" spans="1:2">
       <c r="A1009" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
       <c r="B1009" t="s">
         <v>1722</v>
@@ -14555,36 +14576,36 @@
         <v>1723</v>
       </c>
       <c r="B1010" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="1011" spans="1:2">
       <c r="A1011" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="B1011" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="1012" spans="1:2">
       <c r="A1012" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
       <c r="B1012" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="1013" spans="1:2">
       <c r="A1013" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="B1013" t="s">
-        <v>1728</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="1014" spans="1:2">
       <c r="A1014" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="B1014" t="s">
         <v>1730</v>
@@ -14611,28 +14632,28 @@
         <v>1735</v>
       </c>
       <c r="B1017" t="s">
-        <v>1735</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="1018" spans="1:2">
       <c r="A1018" t="s">
-        <v>1736</v>
+        <v>1737</v>
       </c>
       <c r="B1018" t="s">
-        <v>1736</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="1019" spans="1:2">
       <c r="A1019" t="s">
-        <v>1737</v>
+        <v>1739</v>
       </c>
       <c r="B1019" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="1020" spans="1:2">
       <c r="A1020" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
       <c r="B1020" t="s">
         <v>1740</v>
@@ -14651,44 +14672,44 @@
         <v>1743</v>
       </c>
       <c r="B1022" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="1023" spans="1:2">
       <c r="A1023" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
       <c r="B1023" t="s">
-        <v>1744</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="1024" spans="1:2">
       <c r="A1024" t="s">
-        <v>1745</v>
+        <v>1747</v>
       </c>
       <c r="B1024" t="s">
-        <v>1745</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="1025" spans="1:2">
       <c r="A1025" t="s">
-        <v>1746</v>
+        <v>1748</v>
       </c>
       <c r="B1025" t="s">
-        <v>1746</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="1026" spans="1:2">
       <c r="A1026" t="s">
-        <v>1747</v>
+        <v>1749</v>
       </c>
       <c r="B1026" t="s">
-        <v>1748</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="1027" spans="1:2">
       <c r="A1027" t="s">
-        <v>1749</v>
+        <v>1750</v>
       </c>
       <c r="B1027" t="s">
         <v>1750</v>
@@ -14699,44 +14720,44 @@
         <v>1751</v>
       </c>
       <c r="B1028" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="1029" spans="1:2">
       <c r="A1029" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="B1029" t="s">
-        <v>1753</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="1030" spans="1:2">
       <c r="A1030" t="s">
-        <v>1754</v>
+        <v>1755</v>
       </c>
       <c r="B1030" t="s">
-        <v>1754</v>
+        <v>1755</v>
       </c>
     </row>
     <row r="1031" spans="1:2">
       <c r="A1031" t="s">
-        <v>1755</v>
+        <v>1756</v>
       </c>
       <c r="B1031" t="s">
-        <v>1755</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="1032" spans="1:2">
       <c r="A1032" t="s">
-        <v>1756</v>
+        <v>1758</v>
       </c>
       <c r="B1032" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="1033" spans="1:2">
       <c r="A1033" t="s">
-        <v>1758</v>
+        <v>1759</v>
       </c>
       <c r="B1033" t="s">
         <v>1759</v>
@@ -14803,20 +14824,20 @@
         <v>1774</v>
       </c>
       <c r="B1041" t="s">
-        <v>1774</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="1042" spans="1:2">
       <c r="A1042" t="s">
-        <v>1775</v>
+        <v>1776</v>
       </c>
       <c r="B1042" t="s">
-        <v>1776</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="1043" spans="1:2">
       <c r="A1043" t="s">
-        <v>1777</v>
+        <v>1778</v>
       </c>
       <c r="B1043" t="s">
         <v>1778</v>
@@ -14835,44 +14856,44 @@
         <v>1781</v>
       </c>
       <c r="B1045" t="s">
-        <v>1781</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="1046" spans="1:2">
       <c r="A1046" t="s">
-        <v>1782</v>
+        <v>1783</v>
       </c>
       <c r="B1046" t="s">
-        <v>1782</v>
+        <v>1784</v>
       </c>
     </row>
     <row r="1047" spans="1:2">
       <c r="A1047" t="s">
-        <v>1783</v>
+        <v>1785</v>
       </c>
       <c r="B1047" t="s">
-        <v>1783</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="1048" spans="1:2">
       <c r="A1048" t="s">
-        <v>1784</v>
+        <v>1786</v>
       </c>
       <c r="B1048" t="s">
-        <v>1784</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="1049" spans="1:2">
       <c r="A1049" t="s">
-        <v>1785</v>
+        <v>1787</v>
       </c>
       <c r="B1049" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="1050" spans="1:2">
       <c r="A1050" t="s">
-        <v>1787</v>
+        <v>1788</v>
       </c>
       <c r="B1050" t="s">
         <v>1788</v>
@@ -14883,20 +14904,20 @@
         <v>1789</v>
       </c>
       <c r="B1051" t="s">
-        <v>1789</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="1052" spans="1:2">
       <c r="A1052" t="s">
-        <v>1790</v>
+        <v>1791</v>
       </c>
       <c r="B1052" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="1053" spans="1:2">
       <c r="A1053" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="B1053" t="s">
         <v>1793</v>
@@ -14915,20 +14936,20 @@
         <v>1796</v>
       </c>
       <c r="B1055" t="s">
-        <v>1796</v>
+        <v>1797</v>
       </c>
     </row>
     <row r="1056" spans="1:2">
       <c r="A1056" t="s">
-        <v>1797</v>
+        <v>1798</v>
       </c>
       <c r="B1056" t="s">
-        <v>1798</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="1057" spans="1:2">
       <c r="A1057" t="s">
-        <v>1799</v>
+        <v>1800</v>
       </c>
       <c r="B1057" t="s">
         <v>1800</v>
@@ -14939,20 +14960,20 @@
         <v>1801</v>
       </c>
       <c r="B1058" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
     </row>
     <row r="1059" spans="1:2">
       <c r="A1059" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="B1059" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="1060" spans="1:2">
       <c r="A1060" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
       <c r="B1060" t="s">
         <v>1805</v>
@@ -14971,20 +14992,20 @@
         <v>1808</v>
       </c>
       <c r="B1062" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
     </row>
     <row r="1063" spans="1:2">
       <c r="A1063" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
       <c r="B1063" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
     </row>
     <row r="1064" spans="1:2">
       <c r="A1064" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B1064" t="s">
         <v>1812</v>
@@ -15067,20 +15088,20 @@
         <v>1831</v>
       </c>
       <c r="B1074" t="s">
-        <v>1831</v>
+        <v>1832</v>
       </c>
     </row>
     <row r="1075" spans="1:2">
       <c r="A1075" t="s">
-        <v>1832</v>
+        <v>1833</v>
       </c>
       <c r="B1075" t="s">
-        <v>1833</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="1076" spans="1:2">
       <c r="A1076" t="s">
-        <v>1834</v>
+        <v>1835</v>
       </c>
       <c r="B1076" t="s">
         <v>1835</v>
@@ -15171,76 +15192,76 @@
         <v>1856</v>
       </c>
       <c r="B1087" t="s">
-        <v>1856</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="1088" spans="1:2">
       <c r="A1088" t="s">
-        <v>1857</v>
+        <v>1858</v>
       </c>
       <c r="B1088" t="s">
-        <v>1858</v>
+        <v>1859</v>
       </c>
     </row>
     <row r="1089" spans="1:2">
       <c r="A1089" t="s">
-        <v>1859</v>
+        <v>1860</v>
       </c>
       <c r="B1089" t="s">
-        <v>1859</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="1090" spans="1:2">
       <c r="A1090" t="s">
-        <v>1860</v>
+        <v>1861</v>
       </c>
       <c r="B1090" t="s">
-        <v>1861</v>
+        <v>1862</v>
       </c>
     </row>
     <row r="1091" spans="1:2">
       <c r="A1091" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
       <c r="B1091" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="1092" spans="1:2">
       <c r="A1092" t="s">
-        <v>1863</v>
+        <v>1864</v>
       </c>
       <c r="B1092" t="s">
-        <v>1863</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="1093" spans="1:2">
       <c r="A1093" t="s">
-        <v>1864</v>
+        <v>1866</v>
       </c>
       <c r="B1093" t="s">
-        <v>1865</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="1094" spans="1:2">
       <c r="A1094" t="s">
-        <v>1866</v>
+        <v>1867</v>
       </c>
       <c r="B1094" t="s">
-        <v>1866</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="1095" spans="1:2">
       <c r="A1095" t="s">
-        <v>1867</v>
+        <v>1868</v>
       </c>
       <c r="B1095" t="s">
-        <v>1868</v>
+        <v>1869</v>
       </c>
     </row>
     <row r="1096" spans="1:2">
       <c r="A1096" t="s">
-        <v>1869</v>
+        <v>1870</v>
       </c>
       <c r="B1096" t="s">
         <v>1870</v>
@@ -15251,20 +15272,20 @@
         <v>1871</v>
       </c>
       <c r="B1097" t="s">
-        <v>1871</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="1098" spans="1:2">
       <c r="A1098" t="s">
-        <v>1872</v>
+        <v>1873</v>
       </c>
       <c r="B1098" t="s">
-        <v>1873</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="1099" spans="1:2">
       <c r="A1099" t="s">
-        <v>1874</v>
+        <v>1875</v>
       </c>
       <c r="B1099" t="s">
         <v>1875</v>
@@ -15323,28 +15344,28 @@
         <v>1888</v>
       </c>
       <c r="B1106" t="s">
-        <v>1888</v>
+        <v>1889</v>
       </c>
     </row>
     <row r="1107" spans="1:2">
       <c r="A1107" t="s">
-        <v>1889</v>
+        <v>1890</v>
       </c>
       <c r="B1107" t="s">
-        <v>1889</v>
+        <v>1891</v>
       </c>
     </row>
     <row r="1108" spans="1:2">
       <c r="A1108" t="s">
-        <v>1890</v>
+        <v>1892</v>
       </c>
       <c r="B1108" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
     </row>
     <row r="1109" spans="1:2">
       <c r="A1109" t="s">
-        <v>1892</v>
+        <v>1893</v>
       </c>
       <c r="B1109" t="s">
         <v>1893</v>
@@ -15379,20 +15400,20 @@
         <v>1900</v>
       </c>
       <c r="B1113" t="s">
-        <v>1900</v>
+        <v>1901</v>
       </c>
     </row>
     <row r="1114" spans="1:2">
       <c r="A1114" t="s">
-        <v>1901</v>
+        <v>1902</v>
       </c>
       <c r="B1114" t="s">
-        <v>1902</v>
+        <v>1903</v>
       </c>
     </row>
     <row r="1115" spans="1:2">
       <c r="A1115" t="s">
-        <v>1903</v>
+        <v>1904</v>
       </c>
       <c r="B1115" t="s">
         <v>1904</v>
@@ -15411,44 +15432,44 @@
         <v>1907</v>
       </c>
       <c r="B1117" t="s">
-        <v>1907</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="1118" spans="1:2">
       <c r="A1118" t="s">
-        <v>1908</v>
+        <v>1909</v>
       </c>
       <c r="B1118" t="s">
-        <v>1909</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="1119" spans="1:2">
       <c r="A1119" t="s">
-        <v>1910</v>
+        <v>1911</v>
       </c>
       <c r="B1119" t="s">
-        <v>1910</v>
+        <v>1911</v>
       </c>
     </row>
     <row r="1120" spans="1:2">
       <c r="A1120" t="s">
-        <v>1911</v>
+        <v>1912</v>
       </c>
       <c r="B1120" t="s">
-        <v>1911</v>
+        <v>1912</v>
       </c>
     </row>
     <row r="1121" spans="1:2">
       <c r="A1121" t="s">
-        <v>1912</v>
+        <v>1913</v>
       </c>
       <c r="B1121" t="s">
-        <v>1913</v>
+        <v>1914</v>
       </c>
     </row>
     <row r="1122" spans="1:2">
       <c r="A1122" t="s">
-        <v>1914</v>
+        <v>1915</v>
       </c>
       <c r="B1122" t="s">
         <v>1915</v>
@@ -15459,20 +15480,20 @@
         <v>1916</v>
       </c>
       <c r="B1123" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="1124" spans="1:2">
       <c r="A1124" t="s">
+        <v>1917</v>
+      </c>
+      <c r="B1124" t="s">
         <v>1918</v>
-      </c>
-      <c r="B1124" t="s">
-        <v>1919</v>
       </c>
     </row>
     <row r="1125" spans="1:2">
       <c r="A1125" t="s">
-        <v>1920</v>
+        <v>1919</v>
       </c>
       <c r="B1125" t="s">
         <v>1920</v>
@@ -15491,12 +15512,12 @@
         <v>1923</v>
       </c>
       <c r="B1127" t="s">
-        <v>1923</v>
+        <v>1924</v>
       </c>
     </row>
     <row r="1128" spans="1:2">
       <c r="A1128" t="s">
-        <v>1924</v>
+        <v>1925</v>
       </c>
       <c r="B1128" t="s">
         <v>1925</v>
@@ -15515,140 +15536,140 @@
         <v>1928</v>
       </c>
       <c r="B1130" t="s">
-        <v>1929</v>
+        <v>1928</v>
       </c>
     </row>
     <row r="1131" spans="1:2">
       <c r="A1131" t="s">
+        <v>1929</v>
+      </c>
+      <c r="B1131" t="s">
         <v>1930</v>
-      </c>
-      <c r="B1131" t="s">
-        <v>1931</v>
       </c>
     </row>
     <row r="1132" spans="1:2">
       <c r="A1132" t="s">
+        <v>1931</v>
+      </c>
+      <c r="B1132" t="s">
         <v>1932</v>
-      </c>
-      <c r="B1132" t="s">
-        <v>1933</v>
       </c>
     </row>
     <row r="1133" spans="1:2">
       <c r="A1133" t="s">
+        <v>1933</v>
+      </c>
+      <c r="B1133" t="s">
         <v>1934</v>
-      </c>
-      <c r="B1133" t="s">
-        <v>1935</v>
       </c>
     </row>
     <row r="1134" spans="1:2">
       <c r="A1134" t="s">
+        <v>1935</v>
+      </c>
+      <c r="B1134" t="s">
         <v>1936</v>
-      </c>
-      <c r="B1134" t="s">
-        <v>1937</v>
       </c>
     </row>
     <row r="1135" spans="1:2">
       <c r="A1135" t="s">
+        <v>1937</v>
+      </c>
+      <c r="B1135" t="s">
         <v>1938</v>
-      </c>
-      <c r="B1135" t="s">
-        <v>1939</v>
       </c>
     </row>
     <row r="1136" spans="1:2">
       <c r="A1136" t="s">
+        <v>1939</v>
+      </c>
+      <c r="B1136" t="s">
         <v>1940</v>
-      </c>
-      <c r="B1136" t="s">
-        <v>1941</v>
       </c>
     </row>
     <row r="1137" spans="1:2">
       <c r="A1137" t="s">
+        <v>1941</v>
+      </c>
+      <c r="B1137" t="s">
         <v>1942</v>
-      </c>
-      <c r="B1137" t="s">
-        <v>1943</v>
       </c>
     </row>
     <row r="1138" spans="1:2">
       <c r="A1138" t="s">
+        <v>1943</v>
+      </c>
+      <c r="B1138" t="s">
         <v>1944</v>
-      </c>
-      <c r="B1138" t="s">
-        <v>1945</v>
       </c>
     </row>
     <row r="1139" spans="1:2">
       <c r="A1139" t="s">
+        <v>1945</v>
+      </c>
+      <c r="B1139" t="s">
         <v>1946</v>
-      </c>
-      <c r="B1139" t="s">
-        <v>1947</v>
       </c>
     </row>
     <row r="1140" spans="1:2">
       <c r="A1140" t="s">
+        <v>1947</v>
+      </c>
+      <c r="B1140" t="s">
         <v>1948</v>
-      </c>
-      <c r="B1140" t="s">
-        <v>1949</v>
       </c>
     </row>
     <row r="1141" spans="1:2">
       <c r="A1141" t="s">
+        <v>1949</v>
+      </c>
+      <c r="B1141" t="s">
         <v>1950</v>
-      </c>
-      <c r="B1141" t="s">
-        <v>1951</v>
       </c>
     </row>
     <row r="1142" spans="1:2">
       <c r="A1142" t="s">
+        <v>1951</v>
+      </c>
+      <c r="B1142" t="s">
         <v>1952</v>
-      </c>
-      <c r="B1142" t="s">
-        <v>1953</v>
       </c>
     </row>
     <row r="1143" spans="1:2">
       <c r="A1143" t="s">
+        <v>1953</v>
+      </c>
+      <c r="B1143" t="s">
         <v>1954</v>
-      </c>
-      <c r="B1143" t="s">
-        <v>1955</v>
       </c>
     </row>
     <row r="1144" spans="1:2">
       <c r="A1144" t="s">
+        <v>1955</v>
+      </c>
+      <c r="B1144" t="s">
         <v>1956</v>
-      </c>
-      <c r="B1144" t="s">
-        <v>1957</v>
       </c>
     </row>
     <row r="1145" spans="1:2">
       <c r="A1145" t="s">
+        <v>1957</v>
+      </c>
+      <c r="B1145" t="s">
         <v>1958</v>
-      </c>
-      <c r="B1145" t="s">
-        <v>1959</v>
       </c>
     </row>
     <row r="1146" spans="1:2">
       <c r="A1146" t="s">
+        <v>1959</v>
+      </c>
+      <c r="B1146" t="s">
         <v>1960</v>
-      </c>
-      <c r="B1146" t="s">
-        <v>1961</v>
       </c>
     </row>
     <row r="1147" spans="1:2">
       <c r="A1147" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="B1147" t="s">
         <v>1962</v>
@@ -15659,36 +15680,36 @@
         <v>1963</v>
       </c>
       <c r="B1148" t="s">
-        <v>1963</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="1149" spans="1:2">
       <c r="A1149" t="s">
-        <v>1964</v>
+        <v>1965</v>
       </c>
       <c r="B1149" t="s">
-        <v>1964</v>
+        <v>1966</v>
       </c>
     </row>
     <row r="1150" spans="1:2">
       <c r="A1150" t="s">
-        <v>1965</v>
+        <v>1967</v>
       </c>
       <c r="B1150" t="s">
-        <v>1966</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="1151" spans="1:2">
       <c r="A1151" t="s">
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="B1151" t="s">
-        <v>1967</v>
+        <v>1968</v>
       </c>
     </row>
     <row r="1152" spans="1:2">
       <c r="A1152" t="s">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="B1152" t="s">
         <v>1969</v>
@@ -15715,28 +15736,28 @@
         <v>1973</v>
       </c>
       <c r="B1155" t="s">
-        <v>1973</v>
+        <v>1974</v>
       </c>
     </row>
     <row r="1156" spans="1:2">
       <c r="A1156" t="s">
-        <v>1974</v>
+        <v>1975</v>
       </c>
       <c r="B1156" t="s">
-        <v>1974</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="1157" spans="1:2">
       <c r="A1157" t="s">
-        <v>1975</v>
+        <v>1977</v>
       </c>
       <c r="B1157" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="1158" spans="1:2">
       <c r="A1158" t="s">
-        <v>1977</v>
+        <v>1978</v>
       </c>
       <c r="B1158" t="s">
         <v>1978</v>
@@ -15771,36 +15792,36 @@
         <v>1984</v>
       </c>
       <c r="B1162" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="1163" spans="1:2">
       <c r="A1163" t="s">
+        <v>1985</v>
+      </c>
+      <c r="B1163" t="s">
         <v>1986</v>
-      </c>
-      <c r="B1163" t="s">
-        <v>1987</v>
       </c>
     </row>
     <row r="1164" spans="1:2">
       <c r="A1164" t="s">
+        <v>1987</v>
+      </c>
+      <c r="B1164" t="s">
         <v>1988</v>
-      </c>
-      <c r="B1164" t="s">
-        <v>1989</v>
       </c>
     </row>
     <row r="1165" spans="1:2">
       <c r="A1165" t="s">
+        <v>1989</v>
+      </c>
+      <c r="B1165" t="s">
         <v>1990</v>
-      </c>
-      <c r="B1165" t="s">
-        <v>1991</v>
       </c>
     </row>
     <row r="1166" spans="1:2">
       <c r="A1166" t="s">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="B1166" t="s">
         <v>1992</v>
@@ -15819,12 +15840,12 @@
         <v>1995</v>
       </c>
       <c r="B1168" t="s">
-        <v>1995</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="1169" spans="1:2">
       <c r="A1169" t="s">
-        <v>1996</v>
+        <v>1997</v>
       </c>
       <c r="B1169" t="s">
         <v>1997</v>
@@ -15851,12 +15872,12 @@
         <v>2002</v>
       </c>
       <c r="B1172" t="s">
-        <v>2003</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="1173" spans="1:2">
       <c r="A1173" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="B1173" t="s">
         <v>2004</v>
@@ -15867,44 +15888,44 @@
         <v>2005</v>
       </c>
       <c r="B1174" t="s">
-        <v>2005</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="1175" spans="1:2">
       <c r="A1175" t="s">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="B1175" t="s">
-        <v>2006</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="1176" spans="1:2">
       <c r="A1176" t="s">
-        <v>2007</v>
+        <v>2009</v>
       </c>
       <c r="B1176" t="s">
-        <v>2007</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="1177" spans="1:2">
       <c r="A1177" t="s">
-        <v>2008</v>
+        <v>2011</v>
       </c>
       <c r="B1177" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="1178" spans="1:2">
       <c r="A1178" t="s">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="B1178" t="s">
-        <v>2011</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="1179" spans="1:2">
       <c r="A1179" t="s">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="B1179" t="s">
         <v>2013</v>
@@ -15923,68 +15944,68 @@
         <v>2015</v>
       </c>
       <c r="B1181" t="s">
-        <v>2015</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="1182" spans="1:2">
       <c r="A1182" t="s">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="B1182" t="s">
-        <v>2017</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="1183" spans="1:2">
       <c r="A1183" t="s">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="B1183" t="s">
-        <v>2018</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="1184" spans="1:2">
       <c r="A1184" t="s">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="B1184" t="s">
-        <v>2019</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="1185" spans="1:2">
       <c r="A1185" t="s">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="B1185" t="s">
-        <v>2020</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="1186" spans="1:2">
       <c r="A1186" t="s">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="B1186" t="s">
-        <v>2021</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="1187" spans="1:2">
       <c r="A1187" t="s">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="B1187" t="s">
-        <v>2023</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="1188" spans="1:2">
       <c r="A1188" t="s">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="B1188" t="s">
-        <v>2025</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="1189" spans="1:2">
       <c r="A1189" t="s">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B1189" t="s">
         <v>2027</v>
@@ -15995,12 +16016,12 @@
         <v>2028</v>
       </c>
       <c r="B1190" t="s">
-        <v>2029</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="1191" spans="1:2">
       <c r="A1191" t="s">
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="B1191" t="s">
         <v>2030</v>
@@ -16019,19 +16040,51 @@
         <v>2033</v>
       </c>
       <c r="B1193" t="s">
-        <v>2033</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="1194" spans="1:2">
       <c r="A1194" t="s">
-        <v>2034</v>
+        <v>2035</v>
       </c>
       <c r="B1194" t="s">
-        <v>2035</v>
+        <v>2036</v>
+      </c>
+    </row>
+    <row r="1195" spans="1:2">
+      <c r="A1195" t="s">
+        <v>2037</v>
+      </c>
+      <c r="B1195" t="s">
+        <v>2037</v>
+      </c>
+    </row>
+    <row r="1196" spans="1:2">
+      <c r="A1196" t="s">
+        <v>2038</v>
+      </c>
+      <c r="B1196" t="s">
+        <v>2039</v>
+      </c>
+    </row>
+    <row r="1197" spans="1:2">
+      <c r="A1197" t="s">
+        <v>2040</v>
+      </c>
+      <c r="B1197" t="s">
+        <v>2040</v>
+      </c>
+    </row>
+    <row r="1198" spans="1:2">
+      <c r="A1198" t="s">
+        <v>2041</v>
+      </c>
+      <c r="B1198" t="s">
+        <v>2042</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B1194"/>
+  <autoFilter ref="A1:B1198"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
